--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Rd5cd210ebb184398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R5a04e8321adb4fcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="Rac54d0912d274ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Re9cb2acc3b2f416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R2a0e880284264400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R5b42f2fa938c4cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R031c5c55f9c04b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R312e90e484544bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Rd898866200114639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R6f144dcca86f4f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="Rc54e7f51d27346ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Rb3317623790f4274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R4cbfed1ffbbc41e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R19d9b030fedd4b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R67f3f16688f046d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R1723f3a68fd741f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R65b22a1307f24117"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -3851,96 +3852,6 @@
     <x:t xml:space="preserve">Comments</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Automated backend tests</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pytest output</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">76 pytest checks passed; pip check and compileall passed.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flutter analysis/tests/build</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Command output</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Analyzer clean; 33 tests passed; release web build passed.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">All published assignments validate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Validation report</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Four published versioned assignments passed repository/grader validation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">All official solutions pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Per-assignment evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Assignments 1-4 official solutions passed modular graders.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Desktop/mobile critical path</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Screenshots or test record</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Live Chrome desktop passed; responsive widget tests passed; independent device/accessibility audit remains.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sandbox security checks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Timeout/import/output/resource evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dedicated authenticated sandbox service passes local automated and two-process checks; Render image build and live penetration/resource evidence remain open.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Instructor workflow</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Create/edit/validate/publish evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Live studio/accounts read paths passed; mutation paths passed automated tests but were not executed against production data.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Authentication and account management</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Login, role, session, password, account, audit, and email evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Student/instructor/invalid/session/logout/role/admin checks passed; self-service email reset is out of scope.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Secrets and source diff review</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Git evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No tracked environments or real credentials; one synthetic migration-test URL matched the scanner.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Defect retest complete</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Defect IDs and retest evidence</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No new product defect was found in this SQA cycle.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Approvals</x:t>
   </x:si>
   <x:si>
@@ -4555,7 +4466,7 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -4611,8 +4522,32 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos Narrow"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF153E45"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF137A45"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9A6700"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -4664,8 +4599,28 @@
         <x:fgColor rgb="FFBDD7EE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F5C66"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD8EEF1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF167D8D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F8F9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -4785,12 +4740,26 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB6CDD1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB6CDD1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB6CDD1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB6CDD1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -4948,6 +4917,50 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -9306,7 +9319,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R874b3264efc64d16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4dcade8c7684f4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10428,11 +10441,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R6f672cdc1b3543e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R2563e8e0d55d45a1"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1657c34b4c4216"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5d9394dcce34073"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21453,7 +21466,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e293a57c3aa4947"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab06e18915a43de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21778,6 +21791,124 @@
       </x:c>
       <x:c r="S5" s="20" t="s">
         <x:v>1256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>[x]</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>robotics-assignment-5</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>ROS 2 Mobile Robot Velocity Controller</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="Q6" s="56" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="R6" t="str">
+        <x:v>Maintained ROS answer and grader checks passed in the staging baseline; regression suite passed 2026-08-28.</x:v>
+      </x:c>
+      <x:c r="S6" t="str">
+        <x:v>Only controller.py is editable; the project tree and locked support files remain visible.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>[x]</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>robotics-assignment-6</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>ROS 2 Obstacle Stop Controller</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="Q7" s="56" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="R7" t="str">
+        <x:v>Maintained ROS answer and grader checks passed in the staging baseline; regression suite passed 2026-08-28.</x:v>
+      </x:c>
+      <x:c r="S7" t="str">
+        <x:v>Only controller.py is editable; the project tree and locked support files remain visible.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22011,7 +22142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2dbf3780954331"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdc2898cde147fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40088,7 +40219,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd547c3b5112d4e19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94704f5617f44be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40157,203 +40288,203 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="38.099998474121094" customHeight="1">
-      <x:c r="A5" s="9" t="s">
-        <x:v>1274</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="s">
-        <x:v>1275</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E5" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="s">
-        <x:v>1276</x:v>
+      <x:c r="A5" s="9" t="str">
+        <x:v>Automated backend tests</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>pytest output</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E5" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>182 tests passed; pip check and compileall passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38.099998474121094" customHeight="1">
-      <x:c r="A6" s="9" t="s">
-        <x:v>1277</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="s">
-        <x:v>1278</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E6" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="s">
-        <x:v>1279</x:v>
+      <x:c r="A6" s="9" t="str">
+        <x:v>Flutter analysis/tests/build</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>Command output</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E6" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>Analyzer clean; 51 tests passed; release web build passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38.099998474121094" customHeight="1">
-      <x:c r="A7" s="9" t="s">
-        <x:v>1280</x:v>
-      </x:c>
-      <x:c r="B7" s="9" t="s">
-        <x:v>1281</x:v>
-      </x:c>
-      <x:c r="C7" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E7" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="s">
-        <x:v>1282</x:v>
+      <x:c r="A7" s="9" t="str">
+        <x:v>All published assignments validate</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>Validation report</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E7" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str">
+        <x:v>Six published, versioned assignments remain available after the database migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38.099998474121094" customHeight="1">
-      <x:c r="A8" s="9" t="s">
-        <x:v>1283</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="s">
-        <x:v>1284</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E8" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>1285</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>All official solutions pass</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>Per-assignment evidence</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E8" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str">
+        <x:v>Maintained-answer grading remains covered by the existing assignment and grader regression suite.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38.099998474121094" customHeight="1">
-      <x:c r="A9" s="9" t="s">
-        <x:v>1286</x:v>
-      </x:c>
-      <x:c r="B9" s="9" t="s">
-        <x:v>1287</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E9" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="s">
-        <x:v>1288</x:v>
+      <x:c r="A9" s="9" t="str">
+        <x:v>Desktop/mobile critical path</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>Screenshots or test record</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E9" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str">
+        <x:v>Windows local web smoke and responsive widget tests passed; physical Ubuntu and independent accessibility tests remain open.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38.099998474121094" customHeight="1">
-      <x:c r="A10" s="9" t="s">
-        <x:v>1289</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="s">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E10" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F10" s="9" t="s">
-        <x:v>1291</x:v>
+      <x:c r="A10" s="9" t="str">
+        <x:v>Sandbox security checks</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>Timeout/import/output/resource evidence</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E10" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str">
+        <x:v>Sandbox service healthy; backend security/error regression tests passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38.099998474121094" customHeight="1">
-      <x:c r="A11" s="9" t="s">
-        <x:v>1292</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="s">
-        <x:v>1293</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E11" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="s">
-        <x:v>1294</x:v>
+      <x:c r="A11" s="9" t="str">
+        <x:v>Instructor workflow</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>Account and assignment evidence</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E11" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="str">
+        <x:v>Instructor APIs and UI support student/instructor create, edit, reset, activate, and deactivate flows.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="38.099998474121094" customHeight="1">
-      <x:c r="A12" s="9" t="s">
-        <x:v>1295</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>1296</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E12" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F12" s="9" t="s">
-        <x:v>1297</x:v>
+      <x:c r="A12" s="9" t="str">
+        <x:v>Authentication and account management</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>Role, password, account, and isolation evidence</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E12" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str">
+        <x:v>Default student restored; Dave retained with zero progress; persistent browser progress is scoped by user ID.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="38.099998474121094" customHeight="1">
-      <x:c r="A13" s="9" t="s">
-        <x:v>1298</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>1299</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E13" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F13" s="9" t="s">
-        <x:v>1300</x:v>
+      <x:c r="A13" s="9" t="str">
+        <x:v>Secrets and source diff review</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>Git evidence</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E13" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="str">
+        <x:v>Neon URL, private account JSON, dumps, reports, environments, and generated artifacts remain ignored.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38.099998474121094" customHeight="1">
-      <x:c r="A14" s="9" t="s">
-        <x:v>1301</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>1302</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D14" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="E14" s="10">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="s">
-        <x:v>1303</x:v>
+      <x:c r="A14" s="9" t="str">
+        <x:v>Defect retest complete</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="str">
+        <x:v>Defect IDs and retest evidence</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="str">
+        <x:v>SQA</x:v>
+      </x:c>
+      <x:c r="E14" s="53" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="str">
+        <x:v>Cross-account progress contamination was fixed and covered by a dedicated regression test.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -40366,7 +40497,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="50" t="s">
-        <x:v>1304</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="B16" s="50"/>
       <x:c r="C16" s="50"/>
@@ -40376,10 +40507,10 @@
     </x:row>
     <x:row r="17" ht="33.95000076293945" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>1305</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>1306</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
         <x:v>14</x:v>
@@ -40388,7 +40519,7 @@
         <x:v>1272</x:v>
       </x:c>
       <x:c r="E17" s="6" t="s">
-        <x:v>1307</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="F17" s="6" t="s">
         <x:v>1273</x:v>
@@ -40396,11 +40527,11 @@
     </x:row>
     <x:row r="18" ht="38.099998474121094" customHeight="1">
       <x:c r="A18" s="26" t="s">
-        <x:v>1308</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="B18" s="26"/>
       <x:c r="C18" s="26" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D18" s="27"/>
       <x:c r="E18" s="26"/>
@@ -40408,11 +40539,11 @@
     </x:row>
     <x:row r="19" ht="38.099998474121094" customHeight="1">
       <x:c r="A19" s="26" t="s">
-        <x:v>1310</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="B19" s="26"/>
       <x:c r="C19" s="26" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D19" s="27"/>
       <x:c r="E19" s="26"/>
@@ -40420,11 +40551,11 @@
     </x:row>
     <x:row r="20" ht="38.099998474121094" customHeight="1">
       <x:c r="A20" s="26" t="s">
-        <x:v>1311</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="B20" s="26"/>
       <x:c r="C20" s="26" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D20" s="27"/>
       <x:c r="E20" s="26"/>
@@ -40432,11 +40563,11 @@
     </x:row>
     <x:row r="21" ht="38.099998474121094" customHeight="1">
       <x:c r="A21" s="26" t="s">
-        <x:v>1312</x:v>
+        <x:v>1282</x:v>
       </x:c>
       <x:c r="B21" s="26"/>
       <x:c r="C21" s="26" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D21" s="27"/>
       <x:c r="E21" s="26"/>
@@ -40444,11 +40575,11 @@
     </x:row>
     <x:row r="22" ht="38.099998474121094" customHeight="1">
       <x:c r="A22" s="26" t="s">
-        <x:v>1313</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="B22" s="26"/>
       <x:c r="C22" s="26" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="D22" s="27"/>
       <x:c r="E22" s="26"/>
@@ -40507,7 +40638,7 @@
   <x:sheetData>
     <x:row r="1" ht="33.95000076293945" customHeight="1">
       <x:c r="A1" s="48" t="s">
-        <x:v>1314</x:v>
+        <x:v>1284</x:v>
       </x:c>
       <x:c r="B1" s="48"/>
       <x:c r="C1" s="48"/>
@@ -40515,7 +40646,7 @@
     </x:row>
     <x:row r="2" ht="38.099998474121094" customHeight="1">
       <x:c r="A2" s="49" t="s">
-        <x:v>1315</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="B2" s="49"/>
       <x:c r="C2" s="49"/>
@@ -40529,13 +40660,13 @@
     </x:row>
     <x:row r="4" ht="33.95000076293945" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>1316</x:v>
+        <x:v>1286</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>1317</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>1318</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>263</x:v>
@@ -40543,226 +40674,226 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="9" t="s">
-        <x:v>1319</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B5" s="9" t="s">
-        <x:v>1320</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="C5" s="9" t="s">
-        <x:v>1321</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="D5" s="9" t="s">
-        <x:v>1322</x:v>
+        <x:v>1292</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="9" t="s">
-        <x:v>1319</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B6" s="9" t="s">
-        <x:v>1323</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="C6" s="9" t="s">
-        <x:v>1324</x:v>
+        <x:v>1294</x:v>
       </x:c>
       <x:c r="D6" s="9" t="s">
-        <x:v>1325</x:v>
+        <x:v>1295</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="9" t="s">
-        <x:v>1319</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="B7" s="9" t="s">
-        <x:v>1326</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="C7" s="9" t="s">
-        <x:v>1327</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="D7" s="9" t="s">
-        <x:v>1328</x:v>
+        <x:v>1298</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="9" t="s">
-        <x:v>1329</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="B8" s="9" t="s">
-        <x:v>1330</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="C8" s="9" t="s">
-        <x:v>1331</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="D8" s="9" t="s">
-        <x:v>1332</x:v>
+        <x:v>1302</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="9" t="s">
-        <x:v>1329</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="B9" s="9" t="s">
-        <x:v>1333</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="C9" s="9" t="s">
-        <x:v>1334</x:v>
+        <x:v>1304</x:v>
       </x:c>
       <x:c r="D9" s="9" t="s">
-        <x:v>1335</x:v>
+        <x:v>1305</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="9" t="s">
-        <x:v>1336</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
-        <x:v>1337</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="C10" s="9" t="s">
-        <x:v>1338</x:v>
+        <x:v>1308</x:v>
       </x:c>
       <x:c r="D10" s="9" t="s">
-        <x:v>1339</x:v>
+        <x:v>1309</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="9" t="s">
-        <x:v>1336</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="B11" s="9" t="s">
-        <x:v>1340</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="C11" s="9" t="s">
-        <x:v>1341</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="D11" s="9" t="s">
-        <x:v>1342</x:v>
+        <x:v>1312</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="9" t="s">
-        <x:v>1336</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>1343</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>1344</x:v>
+        <x:v>1314</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>1345</x:v>
+        <x:v>1315</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="9" t="s">
-        <x:v>1346</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>1347</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>1348</x:v>
+        <x:v>1318</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>1349</x:v>
+        <x:v>1319</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="9" t="s">
-        <x:v>1346</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="B14" s="9" t="s">
-        <x:v>1350</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>1351</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="D14" s="9" t="s">
-        <x:v>1352</x:v>
+        <x:v>1322</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="9" t="s">
-        <x:v>1346</x:v>
+        <x:v>1316</x:v>
       </x:c>
       <x:c r="B15" s="9" t="s">
-        <x:v>1353</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>1354</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>1355</x:v>
+        <x:v>1325</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="9" t="s">
-        <x:v>1356</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="B16" s="9" t="s">
-        <x:v>1357</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>1358</x:v>
+        <x:v>1328</x:v>
       </x:c>
       <x:c r="D16" s="9" t="s">
-        <x:v>1359</x:v>
+        <x:v>1329</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="9" t="s">
-        <x:v>1356</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="B17" s="9" t="s">
-        <x:v>1360</x:v>
+        <x:v>1330</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>1361</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="D17" s="9" t="s">
-        <x:v>1362</x:v>
+        <x:v>1332</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="9" t="s">
-        <x:v>1356</x:v>
+        <x:v>1326</x:v>
       </x:c>
       <x:c r="B18" s="9" t="s">
-        <x:v>1363</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>1364</x:v>
+        <x:v>1334</x:v>
       </x:c>
       <x:c r="D18" s="9" t="s">
-        <x:v>1365</x:v>
+        <x:v>1335</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="9" t="s">
-        <x:v>1366</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="B19" s="9" t="s">
-        <x:v>1367</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>1368</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="D19" s="9" t="s">
-        <x:v>1369</x:v>
+        <x:v>1339</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="9" t="s">
-        <x:v>1366</x:v>
+        <x:v>1336</x:v>
       </x:c>
       <x:c r="B20" s="9" t="s">
-        <x:v>1370</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>1371</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="D20" s="9" t="s">
-        <x:v>1372</x:v>
+        <x:v>1342</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
@@ -40770,13 +40901,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B21" s="9" t="s">
-        <x:v>1373</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>1374</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="D21" s="9" t="s">
-        <x:v>1375</x:v>
+        <x:v>1345</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
@@ -40784,13 +40915,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="9" t="s">
-        <x:v>1376</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>1377</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="D22" s="9" t="s">
-        <x:v>1378</x:v>
+        <x:v>1348</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
@@ -40798,83 +40929,83 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" s="9" t="s">
-        <x:v>1379</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="C23" s="9" t="s">
-        <x:v>1380</x:v>
+        <x:v>1350</x:v>
       </x:c>
       <x:c r="D23" s="9" t="s">
-        <x:v>1381</x:v>
+        <x:v>1351</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="9" t="s">
-        <x:v>1382</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="B24" s="9" t="s">
-        <x:v>1383</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="C24" s="9" t="s">
-        <x:v>1384</x:v>
+        <x:v>1354</x:v>
       </x:c>
       <x:c r="D24" s="9" t="s">
-        <x:v>1385</x:v>
+        <x:v>1355</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="21" t="s">
-        <x:v>1386</x:v>
+        <x:v>1356</x:v>
       </x:c>
       <x:c r="B25" s="9" t="s">
-        <x:v>1387</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="C25" s="9" t="s">
-        <x:v>1388</x:v>
+        <x:v>1358</x:v>
       </x:c>
       <x:c r="D25" s="19" t="s">
-        <x:v>1389</x:v>
+        <x:v>1359</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27">
       <x:c r="A26" s="21" t="s">
-        <x:v>1390</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>1391</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
-        <x:v>1392</x:v>
+        <x:v>1362</x:v>
       </x:c>
       <x:c r="D26" s="19" t="s">
-        <x:v>1393</x:v>
+        <x:v>1363</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27">
       <x:c r="A27" s="21" t="s">
-        <x:v>1394</x:v>
+        <x:v>1364</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>1395</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>1396</x:v>
+        <x:v>1366</x:v>
       </x:c>
       <x:c r="D27" s="19" t="s">
-        <x:v>1397</x:v>
+        <x:v>1367</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27">
       <x:c r="A28" s="21" t="s">
-        <x:v>1398</x:v>
+        <x:v>1368</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
-        <x:v>1399</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="C28" s="9" t="s">
-        <x:v>1400</x:v>
+        <x:v>1370</x:v>
       </x:c>
       <x:c r="D28" s="19" t="s">
-        <x:v>1401</x:v>
+        <x:v>1371</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -40882,214 +41013,214 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B29" s="9" t="s">
-        <x:v>1402</x:v>
+        <x:v>1372</x:v>
       </x:c>
       <x:c r="C29" s="9" t="s">
-        <x:v>1403</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="D29" s="9" t="s">
-        <x:v>1404</x:v>
+        <x:v>1374</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="33.95000076293945" customHeight="1">
       <x:c r="A30" s="21" t="s">
-        <x:v>1405</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="B30" s="9" t="s">
-        <x:v>1406</x:v>
+        <x:v>1376</x:v>
       </x:c>
       <x:c r="C30" s="9" t="s">
-        <x:v>1407</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="D30" s="19" t="s">
-        <x:v>1408</x:v>
+        <x:v>1378</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="27">
       <x:c r="A31" s="21" t="s">
-        <x:v>1405</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="B31" s="9" t="s">
-        <x:v>1409</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="C31" s="9" t="s">
-        <x:v>1410</x:v>
+        <x:v>1380</x:v>
       </x:c>
       <x:c r="D31" s="19" t="s">
-        <x:v>1411</x:v>
+        <x:v>1381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="27">
       <x:c r="A32" s="21" t="s">
-        <x:v>1405</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="B32" s="9" t="s">
-        <x:v>1412</x:v>
+        <x:v>1382</x:v>
       </x:c>
       <x:c r="C32" s="9" t="s">
-        <x:v>1413</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D32" s="19" t="s">
-        <x:v>1414</x:v>
+        <x:v>1384</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="27">
       <x:c r="A33" s="21" t="s">
-        <x:v>1415</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="B33" s="9" t="s">
-        <x:v>1416</x:v>
+        <x:v>1386</x:v>
       </x:c>
       <x:c r="C33" s="9" t="s">
-        <x:v>1417</x:v>
+        <x:v>1387</x:v>
       </x:c>
       <x:c r="D33" s="19" t="s">
-        <x:v>1418</x:v>
+        <x:v>1388</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="22" t="s">
-        <x:v>1419</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="B34" s="13" t="s">
-        <x:v>1420</x:v>
+        <x:v>1390</x:v>
       </x:c>
       <x:c r="C34" s="13" t="s">
-        <x:v>1421</x:v>
+        <x:v>1391</x:v>
       </x:c>
       <x:c r="D34" s="20" t="s">
-        <x:v>1422</x:v>
+        <x:v>1392</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="22" t="s">
-        <x:v>1419</x:v>
+        <x:v>1389</x:v>
       </x:c>
       <x:c r="B35" s="13" t="s">
-        <x:v>1423</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="C35" s="13" t="s">
-        <x:v>1424</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="D35" s="20" t="s">
-        <x:v>1425</x:v>
+        <x:v>1395</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="22" t="s">
-        <x:v>1426</x:v>
+        <x:v>1396</x:v>
       </x:c>
       <x:c r="B36" s="13" t="s">
-        <x:v>1427</x:v>
+        <x:v>1397</x:v>
       </x:c>
       <x:c r="C36" s="13" t="s">
-        <x:v>1428</x:v>
+        <x:v>1398</x:v>
       </x:c>
       <x:c r="D36" s="20" t="s">
-        <x:v>1429</x:v>
+        <x:v>1399</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="33.95000076293945" customHeight="1">
       <x:c r="A37" s="21" t="s">
-        <x:v>1430</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="B37" s="9" t="s">
-        <x:v>1431</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="C37" s="9" t="s">
-        <x:v>1432</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="D37" s="19" t="s">
-        <x:v>1433</x:v>
+        <x:v>1403</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="33.95000076293945" customHeight="1">
       <x:c r="A38" s="21" t="s">
-        <x:v>1430</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="B38" s="9" t="s">
-        <x:v>1434</x:v>
+        <x:v>1404</x:v>
       </x:c>
       <x:c r="C38" s="9" t="s">
-        <x:v>1435</x:v>
+        <x:v>1405</x:v>
       </x:c>
       <x:c r="D38" s="19" t="s">
-        <x:v>1436</x:v>
+        <x:v>1406</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="33.95000076293945" customHeight="1">
       <x:c r="A39" s="21" t="s">
-        <x:v>1430</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="B39" s="9" t="s">
-        <x:v>1437</x:v>
+        <x:v>1407</x:v>
       </x:c>
       <x:c r="C39" s="9" t="s">
-        <x:v>1438</x:v>
+        <x:v>1408</x:v>
       </x:c>
       <x:c r="D39" s="19" t="s">
-        <x:v>1439</x:v>
+        <x:v>1409</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="33.95000076293945" customHeight="1">
       <x:c r="A40" s="21" t="s">
-        <x:v>1440</x:v>
+        <x:v>1410</x:v>
       </x:c>
       <x:c r="B40" s="9" t="s">
-        <x:v>1441</x:v>
+        <x:v>1411</x:v>
       </x:c>
       <x:c r="C40" s="9" t="s">
-        <x:v>1442</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="D40" s="19" t="s">
-        <x:v>1443</x:v>
+        <x:v>1413</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="33.95000076293945" customHeight="1">
       <x:c r="A41" s="21" t="s">
-        <x:v>1444</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="B41" s="9" t="s">
-        <x:v>1445</x:v>
+        <x:v>1415</x:v>
       </x:c>
       <x:c r="C41" s="9" t="s">
-        <x:v>1446</x:v>
+        <x:v>1416</x:v>
       </x:c>
       <x:c r="D41" s="19" t="s">
-        <x:v>1447</x:v>
+        <x:v>1417</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="33.95000076293945" customHeight="1">
       <x:c r="A42" s="21" t="s">
-        <x:v>1448</x:v>
+        <x:v>1418</x:v>
       </x:c>
       <x:c r="B42" s="9" t="s">
-        <x:v>1449</x:v>
+        <x:v>1419</x:v>
       </x:c>
       <x:c r="C42" s="9" t="s">
-        <x:v>1450</x:v>
+        <x:v>1420</x:v>
       </x:c>
       <x:c r="D42" s="19" t="s">
-        <x:v>1451</x:v>
+        <x:v>1421</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="33.95000076293945" customHeight="1">
       <x:c r="A43" s="21" t="s">
-        <x:v>1452</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="B43" s="9" t="s">
-        <x:v>1453</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="C43" s="9" t="s">
-        <x:v>1454</x:v>
+        <x:v>1424</x:v>
       </x:c>
       <x:c r="D43" s="19" t="s">
-        <x:v>1455</x:v>
+        <x:v>1425</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="25" t="s">
-        <x:v>1456</x:v>
+        <x:v>1426</x:v>
       </x:c>
       <x:c r="B44" s="23"/>
       <x:c r="C44" s="23"/>
@@ -41100,69 +41231,69 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B45" s="7" t="s">
-        <x:v>1457</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="C45" s="7" t="s">
-        <x:v>1458</x:v>
+        <x:v>1428</x:v>
       </x:c>
       <x:c r="D45" s="7" t="s">
-        <x:v>1459</x:v>
+        <x:v>1429</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="40.5">
       <x:c r="A46" s="9" t="s">
-        <x:v>1460</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="B46" s="9" t="s">
-        <x:v>1461</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="C46" s="9" t="s">
-        <x:v>1462</x:v>
+        <x:v>1432</x:v>
       </x:c>
       <x:c r="D46" s="9" t="s">
-        <x:v>1463</x:v>
+        <x:v>1433</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="40.5">
       <x:c r="A47" s="9" t="s">
-        <x:v>1464</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="B47" s="9" t="s">
-        <x:v>1465</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="C47" s="9" t="s">
-        <x:v>1466</x:v>
+        <x:v>1436</x:v>
       </x:c>
       <x:c r="D47" s="9" t="s">
-        <x:v>1467</x:v>
+        <x:v>1437</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="27">
       <x:c r="A48" s="9" t="s">
-        <x:v>1468</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="B48" s="9" t="s">
-        <x:v>1469</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="C48" s="9" t="s">
-        <x:v>1470</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="D48" s="9" t="s">
-        <x:v>1471</x:v>
+        <x:v>1441</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="27">
       <x:c r="A49" s="9" t="s">
-        <x:v>1472</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="B49" s="9" t="s">
-        <x:v>1473</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="C49" s="9" t="s">
-        <x:v>1474</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="D49" s="9" t="s">
-        <x:v>1475</x:v>
+        <x:v>1445</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -41170,13 +41301,13 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B50" s="9" t="s">
-        <x:v>1476</x:v>
+        <x:v>1446</x:v>
       </x:c>
       <x:c r="C50" s="9" t="s">
-        <x:v>1477</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="D50" s="9" t="s">
-        <x:v>1478</x:v>
+        <x:v>1448</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="27">
@@ -41184,13 +41315,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="9" t="s">
-        <x:v>1479</x:v>
+        <x:v>1449</x:v>
       </x:c>
       <x:c r="C51" s="9" t="s">
-        <x:v>1480</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="D51" s="9" t="s">
-        <x:v>1481</x:v>
+        <x:v>1451</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="27">
@@ -41198,13 +41329,13 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B52" s="9" t="s">
-        <x:v>1482</x:v>
+        <x:v>1452</x:v>
       </x:c>
       <x:c r="C52" s="9" t="s">
-        <x:v>1483</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="D52" s="9" t="s">
-        <x:v>1484</x:v>
+        <x:v>1454</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="27">
@@ -41212,13 +41343,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B53" s="9" t="s">
-        <x:v>1485</x:v>
+        <x:v>1455</x:v>
       </x:c>
       <x:c r="C53" s="9" t="s">
-        <x:v>1486</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="D53" s="9" t="s">
-        <x:v>1487</x:v>
+        <x:v>1457</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="27">
@@ -41226,13 +41357,13 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B54" s="9" t="s">
-        <x:v>1488</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="C54" s="9" t="s">
-        <x:v>1489</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="D54" s="9" t="s">
-        <x:v>1490</x:v>
+        <x:v>1460</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27">
@@ -41240,13 +41371,13 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B55" s="9" t="s">
-        <x:v>1491</x:v>
+        <x:v>1461</x:v>
       </x:c>
       <x:c r="C55" s="9" t="s">
-        <x:v>1492</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="D55" s="9" t="s">
-        <x:v>1493</x:v>
+        <x:v>1463</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -41256,7 +41387,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04351ff98a164c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d0d278080c4411"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41276,16 +41407,16 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>1494</x:v>
+        <x:v>1464</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>1495</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>1382</x:v>
+        <x:v>1352</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>1496</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="G1" t="s">
         <x:v>1257</x:v>
@@ -41317,13 +41448,13 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>1497</x:v>
+        <x:v>1467</x:v>
       </x:c>
       <x:c r="G2" t="s">
-        <x:v>1460</x:v>
+        <x:v>1430</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>1309</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="I2" t="s">
         <x:v>276</x:v>
@@ -41349,13 +41480,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>1498</x:v>
+        <x:v>1468</x:v>
       </x:c>
       <x:c r="G3" t="s">
-        <x:v>1464</x:v>
+        <x:v>1434</x:v>
       </x:c>
       <x:c r="H3" t="s">
-        <x:v>1499</x:v>
+        <x:v>1469</x:v>
       </x:c>
       <x:c r="I3" t="s">
         <x:v>1169</x:v>
@@ -41378,13 +41509,13 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>1500</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="G4" t="s">
-        <x:v>1468</x:v>
+        <x:v>1438</x:v>
       </x:c>
       <x:c r="H4" t="s">
-        <x:v>1501</x:v>
+        <x:v>1471</x:v>
       </x:c>
       <x:c r="J4" t="s">
         <x:v>380</x:v>
@@ -41401,16 +41532,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>1502</x:v>
+        <x:v>1472</x:v>
       </x:c>
       <x:c r="G5" t="s">
-        <x:v>1472</x:v>
+        <x:v>1442</x:v>
       </x:c>
       <x:c r="H5" t="s">
-        <x:v>1503</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="J5" t="s">
-        <x:v>1504</x:v>
+        <x:v>1474</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -41437,7 +41568,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="J8" t="s">
-        <x:v>1505</x:v>
+        <x:v>1475</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -41453,4 +41584,394 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
+      <x:c r="A1" s="59" t="str">
+        <x:v>V5.2 Neon and Account Management - SQA Evidence</x:v>
+      </x:c>
+      <x:c r="B1" s="59"/>
+      <x:c r="C1" s="59"/>
+      <x:c r="D1" s="59"/>
+      <x:c r="E1" s="59"/>
+      <x:c r="F1" s="59"/>
+      <x:c r="G1" s="59"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="61" t="str">
+        <x:v>Windows local staging verification | 2026-08-28 | Not committed or pushed</x:v>
+      </x:c>
+      <x:c r="B2" s="61"/>
+      <x:c r="C2" s="61"/>
+      <x:c r="D2" s="61"/>
+      <x:c r="E2" s="61"/>
+      <x:c r="F2" s="61"/>
+      <x:c r="G2" s="61"/>
+    </x:row>
+    <x:row r="3"/>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="65" t="str">
+        <x:v>Check ID</x:v>
+      </x:c>
+      <x:c r="B4" s="65" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="C4" s="65" t="str">
+        <x:v>Verification</x:v>
+      </x:c>
+      <x:c r="D4" s="65" t="str">
+        <x:v>Expected</x:v>
+      </x:c>
+      <x:c r="E4" s="65" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="F4" s="65" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="G4" s="65" t="str">
+        <x:v>Limitation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="68" t="str">
+        <x:v>V52-001</x:v>
+      </x:c>
+      <x:c r="B5" s="68" t="str">
+        <x:v>Neon</x:v>
+      </x:c>
+      <x:c r="C5" s="68" t="str">
+        <x:v>Dedicated staging database</x:v>
+      </x:c>
+      <x:c r="D5" s="68" t="str">
+        <x:v>Use robotics_lab_staging without altering old neondb</x:v>
+      </x:c>
+      <x:c r="E5" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F5" s="68" t="str">
+        <x:v>Launcher selected dedicated Neon database; old database was preserved.</x:v>
+      </x:c>
+      <x:c r="G5" s="68" t="str">
+        <x:v>Internet and Neon availability are required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="69" t="str">
+        <x:v>V52-002</x:v>
+      </x:c>
+      <x:c r="B6" s="69" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="C6" s="69" t="str">
+        <x:v>Local-to-Neon transfer</x:v>
+      </x:c>
+      <x:c r="D6" s="69" t="str">
+        <x:v>All application records migrate</x:v>
+      </x:c>
+      <x:c r="E6" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F6" s="69" t="str">
+        <x:v>376 rows migrated across 10 application tables.</x:v>
+      </x:c>
+      <x:c r="G6" s="69" t="str">
+        <x:v>Migration report remains private.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A7" s="68" t="str">
+        <x:v>V52-003</x:v>
+      </x:c>
+      <x:c r="B7" s="68" t="str">
+        <x:v>Persistence</x:v>
+      </x:c>
+      <x:c r="C7" s="68" t="str">
+        <x:v>Neon restart</x:v>
+      </x:c>
+      <x:c r="D7" s="68" t="str">
+        <x:v>Counts and study history survive restart</x:v>
+      </x:c>
+      <x:c r="E7" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F7" s="68" t="str">
+        <x:v>3 users, 6 assignments, 65 submissions, 2 activities, 44 events, and 22 sessions before and after restart.</x:v>
+      </x:c>
+      <x:c r="G7" s="68" t="str">
+        <x:v>No public deployment was performed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="69" t="str">
+        <x:v>V52-004</x:v>
+      </x:c>
+      <x:c r="B8" s="69" t="str">
+        <x:v>Accounts</x:v>
+      </x:c>
+      <x:c r="C8" s="69" t="str">
+        <x:v>Default student credential</x:v>
+      </x:c>
+      <x:c r="D8" s="69" t="str">
+        <x:v>Required prototype credential verifies</x:v>
+      </x:c>
+      <x:c r="E8" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F8" s="69" t="str">
+        <x:v>Password hash verified without writing plaintext to the workbook.</x:v>
+      </x:c>
+      <x:c r="G8" s="69" t="str">
+        <x:v>Change before a real classroom study.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="68" t="str">
+        <x:v>V52-005</x:v>
+      </x:c>
+      <x:c r="B9" s="68" t="str">
+        <x:v>Accounts</x:v>
+      </x:c>
+      <x:c r="C9" s="68" t="str">
+        <x:v>Dave retained</x:v>
+      </x:c>
+      <x:c r="D9" s="68" t="str">
+        <x:v>Account active with no inherited work</x:v>
+      </x:c>
+      <x:c r="E9" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F9" s="68" t="str">
+        <x:v>0 attempts and 0 completed assignments in Neon.</x:v>
+      </x:c>
+      <x:c r="G9" s="68" t="str">
+        <x:v>A stale browser page must refresh after frontend update.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A10" s="69" t="str">
+        <x:v>V52-006</x:v>
+      </x:c>
+      <x:c r="B10" s="69" t="str">
+        <x:v>Progress</x:v>
+      </x:c>
+      <x:c r="C10" s="69" t="str">
+        <x:v>Cross-account isolation</x:v>
+      </x:c>
+      <x:c r="D10" s="69" t="str">
+        <x:v>One student cannot inherit another student's local progress</x:v>
+      </x:c>
+      <x:c r="E10" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F10" s="69" t="str">
+        <x:v>Dedicated user-ID storage regression test passed.</x:v>
+      </x:c>
+      <x:c r="G10" s="69" t="str">
+        <x:v>Legacy data migrates only to the default prototype student.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A11" s="68" t="str">
+        <x:v>V52-007</x:v>
+      </x:c>
+      <x:c r="B11" s="68" t="str">
+        <x:v>Instructor Studio</x:v>
+      </x:c>
+      <x:c r="C11" s="68" t="str">
+        <x:v>Manage both roles</x:v>
+      </x:c>
+      <x:c r="D11" s="68" t="str">
+        <x:v>Create/list/edit/reset/activate/deactivate students and instructors</x:v>
+      </x:c>
+      <x:c r="E11" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F11" s="68" t="str">
+        <x:v>Backend role flows and Flutter UI regression tests passed.</x:v>
+      </x:c>
+      <x:c r="G11" s="68" t="str">
+        <x:v>Deletion is intentionally replaced with deactivation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="69" t="str">
+        <x:v>V52-008</x:v>
+      </x:c>
+      <x:c r="B12" s="69" t="str">
+        <x:v>Safety</x:v>
+      </x:c>
+      <x:c r="C12" s="69" t="str">
+        <x:v>Instructor lockout prevention</x:v>
+      </x:c>
+      <x:c r="D12" s="69" t="str">
+        <x:v>Cannot self-disable or disable the last active instructor</x:v>
+      </x:c>
+      <x:c r="E12" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F12" s="69" t="str">
+        <x:v>Focused API test passed.</x:v>
+      </x:c>
+      <x:c r="G12" s="69" t="str">
+        <x:v>A second instructor is required before deactivating the first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="68" t="str">
+        <x:v>V52-009</x:v>
+      </x:c>
+      <x:c r="B13" s="68" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C13" s="68" t="str">
+        <x:v>Private account importer</x:v>
+      </x:c>
+      <x:c r="D13" s="68" t="str">
+        <x:v>File changes synchronize safely without deleting history</x:v>
+      </x:c>
+      <x:c r="E13" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F13" s="68" t="str">
+        <x:v>Private JSON is read from local_handoff_package and temporary passwords are cleared after hashing.</x:v>
+      </x:c>
+      <x:c r="G13" s="68" t="str">
+        <x:v>File is ignored by Git because it may contain credentials.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="69" t="str">
+        <x:v>V52-010</x:v>
+      </x:c>
+      <x:c r="B14" s="69" t="str">
+        <x:v>Fallback</x:v>
+      </x:c>
+      <x:c r="C14" s="69" t="str">
+        <x:v>Explicit local PostgreSQL mode</x:v>
+      </x:c>
+      <x:c r="D14" s="69" t="str">
+        <x:v>Offline mode remains usable</x:v>
+      </x:c>
+      <x:c r="E14" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F14" s="69" t="str">
+        <x:v>Frontend/API/sandbox healthy; final verified dump created on stop.</x:v>
+      </x:c>
+      <x:c r="G14" s="69" t="str">
+        <x:v>Fallback snapshot does not continuously sync with Neon.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="68" t="str">
+        <x:v>V52-011</x:v>
+      </x:c>
+      <x:c r="B15" s="68" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="C15" s="68" t="str">
+        <x:v>Full Python gate</x:v>
+      </x:c>
+      <x:c r="D15" s="68" t="str">
+        <x:v>Tests, dependencies, compilation pass</x:v>
+      </x:c>
+      <x:c r="E15" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F15" s="68" t="str">
+        <x:v>182 tests; pip check clean; compileall clean.</x:v>
+      </x:c>
+      <x:c r="G15" s="68" t="str">
+        <x:v>None observed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="69" t="str">
+        <x:v>V52-012</x:v>
+      </x:c>
+      <x:c r="B16" s="69" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="C16" s="69" t="str">
+        <x:v>Full Flutter gate</x:v>
+      </x:c>
+      <x:c r="D16" s="69" t="str">
+        <x:v>Analysis, tests, release build pass</x:v>
+      </x:c>
+      <x:c r="E16" s="73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F16" s="69" t="str">
+        <x:v>Analyzer clean; 51 tests; release web build succeeded.</x:v>
+      </x:c>
+      <x:c r="G16" s="69" t="str">
+        <x:v>Dependency updates were available but not required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="68" t="str">
+        <x:v>V52-013</x:v>
+      </x:c>
+      <x:c r="B17" s="68" t="str">
+        <x:v>Runtime</x:v>
+      </x:c>
+      <x:c r="C17" s="68" t="str">
+        <x:v>Local stack health</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>Frontend, API, and sandbox respond</x:v>
+      </x:c>
+      <x:c r="E17" s="72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="F17" s="68" t="str">
+        <x:v>Frontend HTTP 200; backend and sandbox health status ok.</x:v>
+      </x:c>
+      <x:c r="G17" s="68" t="str">
+        <x:v>Authenticated mutations were validated by API/widget tests to avoid altering shared data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="69" t="str">
+        <x:v>V52-014</x:v>
+      </x:c>
+      <x:c r="B18" s="69" t="str">
+        <x:v>Ubuntu</x:v>
+      </x:c>
+      <x:c r="C18" s="69" t="str">
+        <x:v>Bash/ShellCheck on current host</x:v>
+      </x:c>
+      <x:c r="D18" s="69" t="str">
+        <x:v>Scripts parse and lint</x:v>
+      </x:c>
+      <x:c r="E18" s="75" t="str">
+        <x:v>NOT RUN</x:v>
+      </x:c>
+      <x:c r="F18" s="69" t="str">
+        <x:v>Current Windows host has no Bash/WSL or ShellCheck runtime.</x:v>
+      </x:c>
+      <x:c r="G18" s="69" t="str">
+        <x:v>Physical Ubuntu lab-computer smoke test remains required.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Rd898866200114639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R6f144dcca86f4f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="Rc54e7f51d27346ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Rb3317623790f4274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R4cbfed1ffbbc41e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R19d9b030fedd4b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R67f3f16688f046d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R1723f3a68fd741f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R65b22a1307f24117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="R6f0a1e9d317f4263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R35cef73e2235402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R9c357a8b5ee24f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R636c527b03714035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R69e2490df172448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R68e0163e5a234174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="Rf9756e24bc154631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R0d35607cd0174b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R6b56ff7f83804398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R2f529141c0f04b73"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -4466,7 +4467,7 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -4546,8 +4547,20 @@
       <x:color rgb="FF9A6700"/>
       <x:name val="Aptos Narrow"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF064E3B"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF166534"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -4619,8 +4632,18 @@
         <x:fgColor rgb="FFF3F8F9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="22">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -4754,12 +4777,102 @@
         <x:color rgb="FFB6CDD1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="114">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -4960,6 +5073,94 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="13" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -9319,8 +9520,155 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4dcade8c7684f4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a080bbf51b94c56"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="77" t="str">
+        <x:v>Neon-Only Database Architecture — SQA</x:v>
+      </x:c>
+      <x:c r="B1" s="77"/>
+      <x:c r="C1" s="77"/>
+      <x:c r="D1" s="77"/>
+      <x:c r="E1" s="77"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="80" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="B3" s="80" t="str">
+        <x:v>Verification</x:v>
+      </x:c>
+      <x:c r="C3" s="80" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="D3" s="80" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="E3" s="80" t="str">
+        <x:v>Remaining limitation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A4" s="99" t="str">
+        <x:v>Runtime selection</x:v>
+      </x:c>
+      <x:c r="B4" s="100" t="str">
+        <x:v>Launcher accepts only the configured Neon staging URL</x:v>
+      </x:c>
+      <x:c r="C4" s="111" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D4" s="100" t="str">
+        <x:v>Windows startup and runtime-state verification</x:v>
+      </x:c>
+      <x:c r="E4" s="101" t="str">
+        <x:v>Internet and Neon service required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A5" s="102" t="str">
+        <x:v>Local fallback removal</x:v>
+      </x:c>
+      <x:c r="B5" s="103" t="str">
+        <x:v>PostgreSQL Compose service, dump transfer, backup worker, device lock, and SQLite runtime switches removed</x:v>
+      </x:c>
+      <x:c r="C5" s="112" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D5" s="103" t="str">
+        <x:v>Repository and launcher inspection</x:v>
+      </x:c>
+      <x:c r="E5" s="104" t="str">
+        <x:v>Historical SQA reports remain labeled as superseded evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A6" s="102" t="str">
+        <x:v>Private package</x:v>
+      </x:c>
+      <x:c r="B6" s="103" t="str">
+        <x:v>Only .env, .gitignore, and README remain; account roster is tracked separately without passwords</x:v>
+      </x:c>
+      <x:c r="C6" s="112" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D6" s="103" t="str">
+        <x:v>verify-private-config.ps1 and backend password-rejection test</x:v>
+      </x:c>
+      <x:c r="E6" s="104" t="str">
+        <x:v>Secrets must be provisioned securely on each authorized computer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A7" s="102" t="str">
+        <x:v>Backend regression</x:v>
+      </x:c>
+      <x:c r="B7" s="103" t="str">
+        <x:v>179 backend tests and pip dependency check</x:v>
+      </x:c>
+      <x:c r="C7" s="112" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D7" s="103" t="str">
+        <x:v>Local automated gate on 2026-08-28</x:v>
+      </x:c>
+      <x:c r="E7" s="104" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A8" s="102" t="str">
+        <x:v>Flutter regression</x:v>
+      </x:c>
+      <x:c r="B8" s="103" t="str">
+        <x:v>Static analysis, 51 tests, and release web build</x:v>
+      </x:c>
+      <x:c r="C8" s="112" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D8" s="103" t="str">
+        <x:v>Local automated gate on 2026-08-28</x:v>
+      </x:c>
+      <x:c r="E8" s="104" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A9" s="105" t="str">
+        <x:v>Service health</x:v>
+      </x:c>
+      <x:c r="B9" s="106" t="str">
+        <x:v>Frontend, backend, sandbox, Alembic migration, and Neon selection</x:v>
+      </x:c>
+      <x:c r="C9" s="113" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D9" s="106" t="str">
+        <x:v>Local Windows runtime on ports 8180/5100/5101</x:v>
+      </x:c>
+      <x:c r="E9" s="107" t="str">
+        <x:v>Physical Ubuntu lab-computer smoke test not repeated</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -10441,11 +10789,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R2563e8e0d55d45a1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rc0d7d38dc9c045fc"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5d9394dcce34073"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3066f4c26243ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21466,7 +21814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab06e18915a43de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2cbdad1db504148"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22142,7 +22490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdc2898cde147fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c83092c3214e1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40219,7 +40567,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94704f5617f44be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bd032b84b3a41d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40304,7 +40652,7 @@
         <x:v>46262</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
-        <x:v>182 tests passed; pip check and compileall passed.</x:v>
+        <x:v>179 tests passed with tracked-roster password protection; pip check and compileall passed.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38.099998474121094" customHeight="1">
@@ -41387,7 +41735,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d0d278080c4411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9567927eb964575"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41612,7 +41960,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="61" t="str">
-        <x:v>Windows local staging verification | 2026-08-28 | Not committed or pushed</x:v>
+        <x:v>Windows local staging verification | 2026-08-28 | Implementation: staging main v5.3; final QA follow-up local</x:v>
       </x:c>
       <x:c r="B2" s="61"/>
       <x:c r="C2" s="61"/>
@@ -41837,19 +42185,19 @@
         <x:v>JSON</x:v>
       </x:c>
       <x:c r="C13" s="68" t="str">
-        <x:v>Private account importer</x:v>
+        <x:v>Tracked password-free account roster</x:v>
       </x:c>
       <x:c r="D13" s="68" t="str">
-        <x:v>File changes synchronize safely without deleting history</x:v>
+        <x:v>Every clone receives account metadata while passwords and hashes remain outside Git</x:v>
       </x:c>
       <x:c r="E13" s="72" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F13" s="68" t="str">
-        <x:v>Private JSON is read from local_handoff_package and temporary passwords are cleared after hashing.</x:v>
+        <x:v>backend/data/study_accounts.json contains metadata only; backend rejects temporary passwords in the canonical roster.</x:v>
       </x:c>
       <x:c r="G13" s="68" t="str">
-        <x:v>File is ignored by Git because it may contain credentials.</x:v>
+        <x:v>Create and reset passwords through Instructor Studio; hashes remain in Neon.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -41857,22 +42205,22 @@
         <x:v>V52-010</x:v>
       </x:c>
       <x:c r="B14" s="69" t="str">
-        <x:v>Fallback</x:v>
+        <x:v>Neon</x:v>
       </x:c>
       <x:c r="C14" s="69" t="str">
-        <x:v>Explicit local PostgreSQL mode</x:v>
+        <x:v>Neon-only database runtime</x:v>
       </x:c>
       <x:c r="D14" s="69" t="str">
-        <x:v>Offline mode remains usable</x:v>
+        <x:v>Startup requires the authorized Neon staging database; no local PostgreSQL, dump restore, backup worker, or device lock remains</x:v>
       </x:c>
       <x:c r="E14" s="73" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F14" s="69" t="str">
-        <x:v>Frontend/API/sandbox healthy; final verified dump created on stop.</x:v>
+        <x:v>Windows start/stop, private-config validation, Alembic migration, runtime-state, and service health checks passed. Internet and Neon availability are required.</x:v>
       </x:c>
       <x:c r="G14" s="69" t="str">
-        <x:v>Fallback snapshot does not continuously sync with Neon.</x:v>
+        <x:v>Requires internet access and Neon availability; no offline database mode remains.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -41892,7 +42240,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="F15" s="68" t="str">
-        <x:v>182 tests; pip check clean; compileall clean.</x:v>
+        <x:v>179 tests after retiring obsolete database-transfer coverage and adding tracked-roster password protection; pip check clean; compileall clean.</x:v>
       </x:c>
       <x:c r="G15" s="68" t="str">
         <x:v>None observed.</x:v>

--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="R6f0a1e9d317f4263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R35cef73e2235402c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R9c357a8b5ee24f51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R636c527b03714035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R69e2490df172448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R68e0163e5a234174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="Rf9756e24bc154631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R0d35607cd0174b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R6b56ff7f83804398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R2f529141c0f04b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="R7a9d437e854c4318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R40bcb85935b84a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R4abe26d0e0c947f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R26658c0cd0544b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="Refef22d409ad441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="Rb9150a93d70b4bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="Rc02709079e754899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R2bad74f4a06d40ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R4057fff2478f406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="Rb480ec69a1da4f72"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -9520,7 +9520,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a080bbf51b94c56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8bceb7a9e944c26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9598,10 +9598,10 @@
     </x:row>
     <x:row r="6" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A6" s="102" t="str">
-        <x:v>Private package</x:v>
+        <x:v>Private configuration</x:v>
       </x:c>
       <x:c r="B6" s="103" t="str">
-        <x:v>Only .env, .gitignore, and README remain; account roster is tracked separately without passwords</x:v>
+        <x:v>One ignored repository-root .env; account roster is tracked separately without passwords</x:v>
       </x:c>
       <x:c r="C6" s="112" t="str">
         <x:v>PASS</x:v>
@@ -9610,7 +9610,7 @@
         <x:v>verify-private-config.ps1 and backend password-rejection test</x:v>
       </x:c>
       <x:c r="E6" s="104" t="str">
-        <x:v>Secrets must be provisioned securely on each authorized computer</x:v>
+        <x:v>The .env must be provisioned securely on each authorized computer</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="79.19999694824219" hidden="0" customHeight="1">
@@ -10789,11 +10789,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rc0d7d38dc9c045fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rf4e5e8a433c64bc7"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3066f4c26243ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra50390abfded4f27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21814,7 +21814,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2cbdad1db504148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e8131621184af3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22490,7 +22490,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c83092c3214e1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72f72d005c1d451e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40567,7 +40567,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bd032b84b3a41d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1a60ecea30c4e81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41735,7 +41735,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9567927eb964575"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e41d7fdb6b4955"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="R7a9d437e854c4318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R40bcb85935b84a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R4abe26d0e0c947f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R26658c0cd0544b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="Refef22d409ad441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="Rb9150a93d70b4bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="Rc02709079e754899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R2bad74f4a06d40ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R4057fff2478f406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="Rb480ec69a1da4f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Ra02a1c6288b14acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R398aef92e2d945ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R487603662cae4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R1ab116dcfd8342ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R8223eab16efd48de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="Red87adc71b1c44e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R4f624fae71b942db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R27c4837c5016469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="Ra9b62b9afae647ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R8c702606027f4621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grading Integrity QA" sheetId="12" r:id="Ra42f14a5809a4c32"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -4467,7 +4468,7 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -4559,8 +4560,37 @@
       <x:color rgb="FF166534"/>
       <x:name val="Aptos Narrow"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2F5D31"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -4642,8 +4672,68 @@
         <x:fgColor rgb="FFD1FAE5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="22">
+  <x:borders count="24">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -4867,12 +4957,25 @@
         <x:color rgb="FFD1D5DB"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C6D1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFB8C6D1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C6D1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="114">
+  <x:cellXfs count="157">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -5162,6 +5265,97 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="23" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="27" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="28" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -9520,7 +9714,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8bceb7a9e944c26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8145fec198144cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9668,6 +9862,333 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="148" t="str">
+        <x:v>Assignment grading integrity repair</x:v>
+      </x:c>
+      <x:c r="B1" s="148"/>
+      <x:c r="C1" s="148"/>
+      <x:c r="D1" s="148"/>
+      <x:c r="E1" s="148"/>
+      <x:c r="F1" s="148"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="149" t="str">
+        <x:v>Test date</x:v>
+      </x:c>
+      <x:c r="B2" s="150" t="n">
+        <x:v>46288.791666666664</x:v>
+      </x:c>
+      <x:c r="C2" s="149" t="str">
+        <x:v>Branch</x:v>
+      </x:c>
+      <x:c r="D2" s="151" t="str">
+        <x:v>fix/grading-integrity</x:v>
+      </x:c>
+      <x:c r="E2" s="149" t="str">
+        <x:v>Release state</x:v>
+      </x:c>
+      <x:c r="F2" s="151" t="str">
+        <x:v>Local only; not committed or pushed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="149" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B3" s="151" t="str">
+        <x:v>Assignments 1-6 grading, scoring, feedback, instructor validation, Flutter compatibility, and real ROS 2 execution</x:v>
+      </x:c>
+      <x:c r="C3" s="151"/>
+      <x:c r="D3" s="151"/>
+      <x:c r="E3" s="151"/>
+      <x:c r="F3" s="151"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="114"/>
+      <x:c r="B4" s="114"/>
+      <x:c r="C4" s="114"/>
+      <x:c r="D4" s="114"/>
+      <x:c r="E4" s="114"/>
+      <x:c r="F4" s="114"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="153" t="str">
+        <x:v>Check ID</x:v>
+      </x:c>
+      <x:c r="B5" s="153" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="C5" s="153" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="D5" s="153" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="E5" s="153" t="str">
+        <x:v>Issue repaired</x:v>
+      </x:c>
+      <x:c r="F5" s="153" t="str">
+        <x:v>Remaining limitation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="129" t="str">
+        <x:v>GI-001</x:v>
+      </x:c>
+      <x:c r="B6" s="129" t="str">
+        <x:v>Run endpoint</x:v>
+      </x:c>
+      <x:c r="C6" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D6" s="129" t="str">
+        <x:v>Run and Submit now use the same assignment grader.</x:v>
+      </x:c>
+      <x:c r="E6" s="129" t="str">
+        <x:v>Executable code can no longer receive an automatic 100% Run result.</x:v>
+      </x:c>
+      <x:c r="F6" s="129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="129" t="str">
+        <x:v>GI-002</x:v>
+      </x:c>
+      <x:c r="B7" s="129" t="str">
+        <x:v>Assignment 1</x:v>
+      </x:c>
+      <x:c r="C7" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D7" s="129" t="str">
+        <x:v>Official 100%; mixed 25%; displayed constants rejected.</x:v>
+      </x:c>
+      <x:c r="E7" s="129" t="str">
+        <x:v>Grades a reusable Bug2 function across hidden coordinate scenarios.</x:v>
+      </x:c>
+      <x:c r="F7" s="129" t="str">
+        <x:v>Hidden cases remain server-only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="129" t="str">
+        <x:v>GI-003</x:v>
+      </x:c>
+      <x:c r="B8" s="129" t="str">
+        <x:v>Assignment 2</x:v>
+      </x:c>
+      <x:c r="C8" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D8" s="129" t="str">
+        <x:v>Official 100%; mixed 25%; displayed constants rejected.</x:v>
+      </x:c>
+      <x:c r="E8" s="129" t="str">
+        <x:v>Grades a reusable Bug route function across hidden coordinate scenarios.</x:v>
+      </x:c>
+      <x:c r="F8" s="129" t="str">
+        <x:v>Hidden cases remain server-only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="129" t="str">
+        <x:v>GI-004</x:v>
+      </x:c>
+      <x:c r="B9" s="129" t="str">
+        <x:v>Assignment 3</x:v>
+      </x:c>
+      <x:c r="C9" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D9" s="129" t="str">
+        <x:v>Official 100%; mixed 50%; displayed constants rejected.</x:v>
+      </x:c>
+      <x:c r="E9" s="129" t="str">
+        <x:v>Grades all eight route outputs across cases where either elevator can win.</x:v>
+      </x:c>
+      <x:c r="F9" s="129" t="str">
+        <x:v>Eight 12.5% checks display as a rounded whole percentage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="129" t="str">
+        <x:v>GI-005</x:v>
+      </x:c>
+      <x:c r="B10" s="129" t="str">
+        <x:v>Assignment 4</x:v>
+      </x:c>
+      <x:c r="C10" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D10" s="129" t="str">
+        <x:v>Official 100%; mixed 60%; displayed constants rejected.</x:v>
+      </x:c>
+      <x:c r="E10" s="129" t="str">
+        <x:v>Expanded grading from two 50% checks to five 20% checks.</x:v>
+      </x:c>
+      <x:c r="F10" s="129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="129" t="str">
+        <x:v>GI-006</x:v>
+      </x:c>
+      <x:c r="B11" s="129" t="str">
+        <x:v>Assignment 5 ROS 2</x:v>
+      </x:c>
+      <x:c r="C11" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D11" s="129" t="str">
+        <x:v>Real Docker ROS grader passed 7 of 7 checks.</x:v>
+      </x:c>
+      <x:c r="E11" s="129" t="str">
+        <x:v>Rubric weights now match the behavior-harness weights.</x:v>
+      </x:c>
+      <x:c r="F11" s="129" t="str">
+        <x:v>Docker Desktop Linux containers are required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="129" t="str">
+        <x:v>GI-007</x:v>
+      </x:c>
+      <x:c r="B12" s="129" t="str">
+        <x:v>Assignment 6 ROS 2</x:v>
+      </x:c>
+      <x:c r="C12" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D12" s="129" t="str">
+        <x:v>Real Docker ROS grader passed 9 of 9 checks.</x:v>
+      </x:c>
+      <x:c r="E12" s="129" t="str">
+        <x:v>Rubric weights now match the behavior-harness weights.</x:v>
+      </x:c>
+      <x:c r="F12" s="129" t="str">
+        <x:v>Docker Desktop Linux containers are required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="129" t="str">
+        <x:v>GI-008</x:v>
+      </x:c>
+      <x:c r="B13" s="129" t="str">
+        <x:v>Instructor validation</x:v>
+      </x:c>
+      <x:c r="C13" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D13" s="129" t="str">
+        <x:v>Function-grader assignments validate, edit, and publish in automated tests.</x:v>
+      </x:c>
+      <x:c r="E13" s="129" t="str">
+        <x:v>Assignment Studio recognizes and validates the new grader configuration.</x:v>
+      </x:c>
+      <x:c r="F13" s="129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="129" t="str">
+        <x:v>GI-009</x:v>
+      </x:c>
+      <x:c r="B14" s="129" t="str">
+        <x:v>Backend regression</x:v>
+      </x:c>
+      <x:c r="C14" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D14" s="129" t="str">
+        <x:v>Final backend regression gate passed all 200 tests.</x:v>
+      </x:c>
+      <x:c r="E14" s="129" t="str">
+        <x:v>No backend regression detected.</x:v>
+      </x:c>
+      <x:c r="F14" s="129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="129" t="str">
+        <x:v>GI-010</x:v>
+      </x:c>
+      <x:c r="B15" s="129" t="str">
+        <x:v>Python dependencies</x:v>
+      </x:c>
+      <x:c r="C15" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D15" s="129" t="str">
+        <x:v>pip check reported no broken requirements.</x:v>
+      </x:c>
+      <x:c r="E15" s="129" t="str">
+        <x:v>No dependency conflict detected.</x:v>
+      </x:c>
+      <x:c r="F15" s="129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="129" t="str">
+        <x:v>GI-011</x:v>
+      </x:c>
+      <x:c r="B16" s="129" t="str">
+        <x:v>Flutter client</x:v>
+      </x:c>
+      <x:c r="C16" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D16" s="129" t="str">
+        <x:v>Static analysis passed; 52 tests passed; release web build completed.</x:v>
+      </x:c>
+      <x:c r="E16" s="129" t="str">
+        <x:v>Updated assignment criteria and instructions remain client-compatible.</x:v>
+      </x:c>
+      <x:c r="F16" s="129" t="str">
+        <x:v>No physical mobile-device test was required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="129" t="str">
+        <x:v>GI-012</x:v>
+      </x:c>
+      <x:c r="B17" s="129" t="str">
+        <x:v>Repository state</x:v>
+      </x:c>
+      <x:c r="C17" s="156" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D17" s="129" t="str">
+        <x:v>Changes are isolated on fix/grading-integrity.</x:v>
+      </x:c>
+      <x:c r="E17" s="129" t="str">
+        <x:v>Production and remote main were not modified.</x:v>
+      </x:c>
+      <x:c r="F17" s="129" t="str">
+        <x:v>Commit and push require separate approval.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -10789,11 +11310,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rf4e5e8a433c64bc7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rd54f9bf16d014c0e"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra50390abfded4f27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R381ae7327f2149e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21814,7 +22335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e8131621184af3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa80bd2e90f4066"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22490,7 +23011,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72f72d005c1d451e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b651e71370a4482"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40567,7 +41088,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1a60ecea30c4e81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e9f3e9e6184ba1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41735,7 +42256,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e41d7fdb6b4955"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9f27b413aab4d4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Ra02a1c6288b14acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R398aef92e2d945ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R487603662cae4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="R1ab116dcfd8342ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R8223eab16efd48de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="Red87adc71b1c44e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R4f624fae71b942db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="R27c4837c5016469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="Ra9b62b9afae647ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R8c702606027f4621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grading Integrity QA" sheetId="12" r:id="Ra42f14a5809a4c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Rd158b9fa5f4c4208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R723135846bbf4e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="Rc2b411fcc97740f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Rfb5dadab684d4184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R4df60db466ae4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R5e25eae9ca994776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R46f9b4bf12b9417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="Ra82007c8245f4e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R601f0b0dd9204a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R75b060f5c3c14e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grading Integrity QA" sheetId="12" r:id="Re31f81f2bb56465b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -4975,7 +4975,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="157">
+  <x:cellXfs count="158">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -5356,6 +5356,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="19" fillId="28" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -9714,7 +9717,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8145fec198144cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25ac87975034ed3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10186,6 +10189,86 @@
       </x:c>
       <x:c r="F17" s="129" t="str">
         <x:v>Commit and push require separate approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="52" hidden="0" customHeight="1">
+      <x:c r="A18" s="157" t="str">
+        <x:v>GI-013</x:v>
+      </x:c>
+      <x:c r="B18" s="157" t="str">
+        <x:v>Student mutation matrix</x:v>
+      </x:c>
+      <x:c r="C18" s="157" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D18" s="157" t="str">
+        <x:v>Assignments 1-4 missing/renamed helpers: 0%; Assignment 5 missing publisher: 20%; Assignment 6 missing publisher: 10%</x:v>
+      </x:c>
+      <x:c r="E18" s="157" t="str">
+        <x:v>Broken or incomplete submissions no longer appear to earn a false 100% score</x:v>
+      </x:c>
+      <x:c r="F18" s="157" t="str">
+        <x:v>ROS partial-credit weights are intentional and remain server-authoritative</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="52" hidden="0" customHeight="1">
+      <x:c r="A19" s="157" t="str">
+        <x:v>GI-014</x:v>
+      </x:c>
+      <x:c r="B19" s="157" t="str">
+        <x:v>Edited-code result state</x:v>
+      </x:c>
+      <x:c r="C19" s="157" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D19" s="157" t="str">
+        <x:v>Manual browser QA: correct answer 100%, edit code, stale Results panel hides and header labels the value as Previous score</x:v>
+      </x:c>
+      <x:c r="E19" s="157" t="str">
+        <x:v>A previous successful result can no longer be mistaken for the edited, untested code</x:v>
+      </x:c>
+      <x:c r="F19" s="157" t="str">
+        <x:v>Completed remains a historical achievement after a prior successful attempt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="52" hidden="0" customHeight="1">
+      <x:c r="A20" s="157" t="str">
+        <x:v>GI-015</x:v>
+      </x:c>
+      <x:c r="B20" s="157" t="str">
+        <x:v>Weighted score display</x:v>
+      </x:c>
+      <x:c r="C20" s="157" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D20" s="157" t="str">
+        <x:v>UI uses backend score; check pass rate is displayed separately. Regression test covers 35% score with 1/2 checks</x:v>
+      </x:c>
+      <x:c r="E20" s="157" t="str">
+        <x:v>Frontend no longer replaces assignment-specific weights with an unweighted check fraction</x:v>
+      </x:c>
+      <x:c r="F20" s="157" t="str">
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="52" hidden="0" customHeight="1">
+      <x:c r="A21" s="157" t="str">
+        <x:v>GI-016</x:v>
+      </x:c>
+      <x:c r="B21" s="157" t="str">
+        <x:v>Frontend regression</x:v>
+      </x:c>
+      <x:c r="C21" s="157" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="D21" s="157" t="str">
+        <x:v>Flutter analyze passed; 52 tests passed; release web build passed; narrow-screen feedback test passed</x:v>
+      </x:c>
+      <x:c r="E21" s="157" t="str">
+        <x:v>Student-facing score and stale-result changes were regression checked</x:v>
+      </x:c>
+      <x:c r="F21" s="157" t="str">
+        <x:v>No physical mobile-device test was performed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11310,11 +11393,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="Rd54f9bf16d014c0e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R3055a45e8b4e4c7d"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R381ae7327f2149e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc4cb549a56455c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22335,7 +22418,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa80bd2e90f4066"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fbfeba095114089"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23011,7 +23094,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b651e71370a4482"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd51d5116cdd84f1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41088,7 +41171,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e9f3e9e6184ba1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa49dd4e24f14d99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42256,7 +42339,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9f27b413aab4d4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ce2012cadbb4865"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
+++ b/docs/sqa/Robotics_Programming_Lab_Master_SQA_Checklist.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="Rd158b9fa5f4c4208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R723135846bbf4e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="Rc2b411fcc97740f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Rfb5dadab684d4184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R4df60db466ae4fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R5e25eae9ca994776"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R46f9b4bf12b9417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="Ra82007c8245f4e19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R601f0b0dd9204a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="R75b060f5c3c14e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grading Integrity QA" sheetId="12" r:id="Re31f81f2bb56465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4 SQA Report" sheetId="9" r:id="R31f81606f3cb47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="7" r:id="R6358db9594364187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Checklist" sheetId="6" r:id="R0f40149d12034651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignment Matrix" sheetId="5" r:id="Ra32127f2e67f4148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R850c548d61844327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Sign-off" sheetId="3" r:id="R9b22d6e0391f4842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="2" r:id="R1d6bcc049a994bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="1" r:id="Ra49d18dacc374dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V5.2 Neon &amp; Accounts" sheetId="10" r:id="R0853ba63f9404761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neon Architecture" sheetId="11" r:id="Rb77a41d447114e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grading Integrity QA" sheetId="12" r:id="R8b0caf5b92d9470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V6.2 Workbench" sheetId="13" r:id="R200570e4aa3a4499"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="AutomationOptions">Lists!$C$2:$C$4</x:definedName>
@@ -4468,7 +4469,7 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="21">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -4589,8 +4590,30 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -4730,6 +4753,46 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F4C5C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCDEBF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F8F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F4C5C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCDEBF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F8F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -4975,7 +5038,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="158">
+  <x:cellXfs count="172">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -5358,6 +5421,46 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -9717,7 +9820,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25ac87975034ed3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7d0ba1acca14c99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10270,6 +10373,316 @@
       <x:c r="F21" s="157" t="str">
         <x:v>No physical mobile-device test was performed</x:v>
       </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF19778C"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="168" t="str">
+        <x:v>V6.2 Learning Workbench QA</x:v>
+      </x:c>
+      <x:c r="B1" s="168" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C1" s="168" t="str">
+        <x:v>Staging only</x:v>
+      </x:c>
+      <x:c r="D1" s="168" t="str"/>
+      <x:c r="E1" s="168" t="str"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="B2" s="169" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="C2" s="169" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="D2" s="169" t="str">
+        <x:v>Scope / limitation</x:v>
+      </x:c>
+      <x:c r="E2" s="169" t="str">
+        <x:v>Follow-up</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="170" t="str">
+        <x:v>Backend regression</x:v>
+      </x:c>
+      <x:c r="B3" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C3" s="170" t="str">
+        <x:v>215 tests passed; 80.65 seconds</x:v>
+      </x:c>
+      <x:c r="D3" s="170" t="str">
+        <x:v>Exact staged release snapshot; no paid AI calls</x:v>
+      </x:c>
+      <x:c r="E3" s="170" t="str"/>
+    </x:row>
+    <x:row r="4" ht="56" customHeight="1">
+      <x:c r="A4" s="171" t="str">
+        <x:v>Python dependencies</x:v>
+      </x:c>
+      <x:c r="B4" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C4" s="171" t="str">
+        <x:v>pip check: no broken requirements</x:v>
+      </x:c>
+      <x:c r="D4" s="171" t="str">
+        <x:v>Existing pinned Python environment</x:v>
+      </x:c>
+      <x:c r="E4" s="171" t="str"/>
+    </x:row>
+    <x:row r="5" ht="56" customHeight="1">
+      <x:c r="A5" s="170" t="str">
+        <x:v>Flutter analysis</x:v>
+      </x:c>
+      <x:c r="B5" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C5" s="170" t="str">
+        <x:v>No issues found</x:v>
+      </x:c>
+      <x:c r="D5" s="170" t="str">
+        <x:v>Approved frontend source only</x:v>
+      </x:c>
+      <x:c r="E5" s="170" t="str"/>
+    </x:row>
+    <x:row r="6" ht="56" customHeight="1">
+      <x:c r="A6" s="171" t="str">
+        <x:v>Flutter regression</x:v>
+      </x:c>
+      <x:c r="B6" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C6" s="171" t="str">
+        <x:v>89 tests passed</x:v>
+      </x:c>
+      <x:c r="D6" s="171" t="str">
+        <x:v>Widgets, APIs, contrast, keyboard and responsive states</x:v>
+      </x:c>
+      <x:c r="E6" s="171" t="str"/>
+    </x:row>
+    <x:row r="7" ht="56" customHeight="1">
+      <x:c r="A7" s="170" t="str">
+        <x:v>Release web build</x:v>
+      </x:c>
+      <x:c r="B7" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C7" s="170" t="str">
+        <x:v>Build completed; 52.3 seconds</x:v>
+      </x:c>
+      <x:c r="D7" s="170" t="str">
+        <x:v>Local API at port 5100</x:v>
+      </x:c>
+      <x:c r="E7" s="170" t="str"/>
+    </x:row>
+    <x:row r="8" ht="56" customHeight="1">
+      <x:c r="A8" s="171" t="str">
+        <x:v>ROS assignment 5</x:v>
+      </x:c>
+      <x:c r="B8" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C8" s="171" t="str">
+        <x:v>Maintained answer: 7/7 checks</x:v>
+      </x:c>
+      <x:c r="D8" s="171" t="str">
+        <x:v>Real pinned Docker image</x:v>
+      </x:c>
+      <x:c r="E8" s="171" t="str"/>
+    </x:row>
+    <x:row r="9" ht="56" customHeight="1">
+      <x:c r="A9" s="170" t="str">
+        <x:v>ROS assignment 6</x:v>
+      </x:c>
+      <x:c r="B9" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C9" s="170" t="str">
+        <x:v>Maintained answer: 9/9 checks</x:v>
+      </x:c>
+      <x:c r="D9" s="170" t="str">
+        <x:v>Real pinned Docker image</x:v>
+      </x:c>
+      <x:c r="E9" s="170" t="str"/>
+    </x:row>
+    <x:row r="10" ht="56" customHeight="1">
+      <x:c r="A10" s="171" t="str">
+        <x:v>Persistent student records</x:v>
+      </x:c>
+      <x:c r="B10" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C10" s="171" t="str">
+        <x:v>Student login, saved assignment and quiz progress, study analytics visible</x:v>
+      </x:c>
+      <x:c r="D10" s="171" t="str">
+        <x:v>Read-only browser checks; existing records preserved</x:v>
+      </x:c>
+      <x:c r="E10" s="171" t="str"/>
+    </x:row>
+    <x:row r="11" ht="56" customHeight="1">
+      <x:c r="A11" s="170" t="str">
+        <x:v>Lesson reading and outline</x:v>
+      </x:c>
+      <x:c r="B11" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C11" s="170" t="str">
+        <x:v>Readable bounded text; outline jump to VFH verified in browser</x:v>
+      </x:c>
+      <x:c r="D11" s="170" t="str">
+        <x:v>Authored HTML retained; anchor behavior also widget-tested</x:v>
+      </x:c>
+      <x:c r="E11" s="170" t="str"/>
+    </x:row>
+    <x:row r="12" ht="56" customHeight="1">
+      <x:c r="A12" s="171" t="str">
+        <x:v>Visual contrast and metadata</x:v>
+      </x:c>
+      <x:c r="B12" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C12" s="171" t="str">
+        <x:v>New tinted surfaces meet tested 4.5:1 text contrast; attempt/best/latest badges</x:v>
+      </x:c>
+      <x:c r="D12" s="171" t="str">
+        <x:v>No grading calculations changed</x:v>
+      </x:c>
+      <x:c r="E12" s="171" t="str"/>
+    </x:row>
+    <x:row r="13" ht="56" customHeight="1">
+      <x:c r="A13" s="170" t="str">
+        <x:v>Results dock</x:v>
+      </x:c>
+      <x:c r="B13" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C13" s="170" t="str">
+        <x:v>Desktop opening, drag resizing, minimize/reopen covered by widget tests</x:v>
+      </x:c>
+      <x:c r="D13" s="170" t="str">
+        <x:v>Browser smoke evidence in Markdown report</x:v>
+      </x:c>
+      <x:c r="E13" s="170" t="str"/>
+    </x:row>
+    <x:row r="14" ht="56" customHeight="1">
+      <x:c r="A14" s="171" t="str">
+        <x:v>Recovery states</x:v>
+      </x:c>
+      <x:c r="B14" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C14" s="171" t="str">
+        <x:v>401 session-expired message tested; generic retry preserved</x:v>
+      </x:c>
+      <x:c r="D14" s="171" t="str">
+        <x:v>No automatic account or session mutation</x:v>
+      </x:c>
+      <x:c r="E14" s="171" t="str"/>
+    </x:row>
+    <x:row r="15" ht="56" customHeight="1">
+      <x:c r="A15" s="170" t="str">
+        <x:v>Production / paid AI</x:v>
+      </x:c>
+      <x:c r="B15" s="170" t="str">
+        <x:v>NOT RUN</x:v>
+      </x:c>
+      <x:c r="C15" s="170" t="str">
+        <x:v>No deployment or OpenAI request made</x:v>
+      </x:c>
+      <x:c r="D15" s="170" t="str">
+        <x:v>Not authorized as part of staging visual release</x:v>
+      </x:c>
+      <x:c r="E15" s="170" t="str">
+        <x:v>Separate future gate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="56" customHeight="1">
+      <x:c r="A16" s="171" t="str">
+        <x:v>Physical Ubuntu / hardware</x:v>
+      </x:c>
+      <x:c r="B16" s="171" t="str">
+        <x:v>NOT RUN</x:v>
+      </x:c>
+      <x:c r="C16" s="171" t="str">
+        <x:v>No second-device test performed</x:v>
+      </x:c>
+      <x:c r="D16" s="171" t="str">
+        <x:v>Source UI change only; existing setup scripts unchanged</x:v>
+      </x:c>
+      <x:c r="E16" s="171" t="str">
+        <x:v>Separate device smoke test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="56" customHeight="1">
+      <x:c r="A17" s="170" t="str">
+        <x:v>Unrelated user file moves</x:v>
+      </x:c>
+      <x:c r="B17" s="170" t="str">
+        <x:v>EXCLUDED</x:v>
+      </x:c>
+      <x:c r="C17" s="170" t="str">
+        <x:v>Answer and reference moves plus content-builder edit not staged</x:v>
+      </x:c>
+      <x:c r="D17" s="170" t="str">
+        <x:v>Backend gate ran exported Git index, not dirty answer paths</x:v>
+      </x:c>
+      <x:c r="E17" s="170" t="str">
+        <x:v>User work remains local</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="56" customHeight="1">
+      <x:c r="A18" s="171" t="str">
+        <x:v>Instructor browser smoke</x:v>
+      </x:c>
+      <x:c r="B18" s="171" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C18" s="171" t="str">
+        <x:v>Instructor sign-in, six published assignments in studio and classroom dashboard loaded</x:v>
+      </x:c>
+      <x:c r="D18" s="171" t="str">
+        <x:v>Read-only; no account or assignment changes</x:v>
+      </x:c>
+      <x:c r="E18" s="171" t="str"/>
+    </x:row>
+    <x:row r="19" ht="56" customHeight="1">
+      <x:c r="A19" s="170" t="str">
+        <x:v>Demo grading browser smoke</x:v>
+      </x:c>
+      <x:c r="B19" s="170" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C19" s="170" t="str">
+        <x:v>Assignment 1 starter 0/4; complete solution 4/4; editing beside dock and responsive drawer verified</x:v>
+      </x:c>
+      <x:c r="D19" s="170" t="str">
+        <x:v>Temporary demo only; AI remained off</x:v>
+      </x:c>
+      <x:c r="E19" s="170" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11393,11 +11806,11 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R3055a45e8b4e4c7d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="R14e1868916e44ef5"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc4cb549a56455c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f5e3e0299324b85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22418,7 +22831,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fbfeba095114089"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92773ef52e154369"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23094,7 +23507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd51d5116cdd84f1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8137ac5908e44bef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41171,7 +41584,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa49dd4e24f14d99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ca6a76eb474343"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42339,7 +42752,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ce2012cadbb4865"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff50bd6652e4172"/>
   </x:tableParts>
 </x:worksheet>
 </file>
